--- a/artfynd/A 50080-2021 artfynd.xlsx
+++ b/artfynd/A 50080-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50080-2021 artfynd.xlsx
+++ b/artfynd/A 50080-2021 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>

--- a/artfynd/A 50080-2021 artfynd.xlsx
+++ b/artfynd/A 50080-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99006171</v>
+        <v>104945521</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spaksjön, Dlr</t>
+          <t>norr om Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558012.5630836735</v>
+        <v>558073</v>
       </c>
       <c r="R2" t="n">
-        <v>6760602.934299977</v>
+        <v>6760503</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lever i de fuktiga markerna på flera ställen</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99006189</v>
+        <v>104945525</v>
       </c>
       <c r="B3" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spaksjön, Dlr</t>
+          <t>norr om Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558040.3071731564</v>
+        <v>558177</v>
       </c>
       <c r="R3" t="n">
-        <v>6760601.446127454</v>
+        <v>6760441</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lever i de fuktiga markerna på flera ställen</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,77 +851,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99292030</v>
+        <v>104945523</v>
       </c>
       <c r="B4" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spaksjön, Dlr</t>
+          <t>norr om Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558050.1911775541</v>
+        <v>558139</v>
       </c>
       <c r="R4" t="n">
-        <v>6760621.515046859</v>
+        <v>6760515</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,19 +948,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hedvig Martin Ahlen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,16 +969,11 @@
         <v>99292045</v>
       </c>
       <c r="B5" t="n">
-        <v>56364</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558089.9941875624</v>
+        <v>558090</v>
       </c>
       <c r="R5" t="n">
-        <v>6760626.051165124</v>
+        <v>6760626</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,19 +1038,9 @@
           <t>2020-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,53 +1067,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104945525</v>
+        <v>99292062</v>
       </c>
       <c r="B6" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>norr om Spaksjön, Dlr</t>
+          <t>Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558177.1608814012</v>
+        <v>558006</v>
       </c>
       <c r="R6" t="n">
-        <v>6760441.028599916</v>
+        <v>6760571</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,29 +1136,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1255,62 +1156,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104945521</v>
+        <v>99292719</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>norr om Spaksjön, Dlr</t>
+          <t>Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558072.5582192974</v>
+        <v>557984</v>
       </c>
       <c r="R7" t="n">
-        <v>6760502.922363072</v>
+        <v>6760598</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,22 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,65 +1261,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104945523</v>
+        <v>99006189</v>
       </c>
       <c r="B8" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>norr om Spaksjön, Dlr</t>
+          <t>Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558139.4779875475</v>
+        <v>558041</v>
       </c>
       <c r="R8" t="n">
-        <v>6760514.701059598</v>
+        <v>6760601</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,22 +1343,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lever i de fuktiga markerna på flera ställen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,33 +1362,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hedvig Martin Ahlen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104945520</v>
+        <v>99006171</v>
       </c>
       <c r="B9" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,37 +1392,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>norr om Spaksjön, Dlr</t>
+          <t>Spaksjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558077.9803881978</v>
+        <v>558012</v>
       </c>
       <c r="R9" t="n">
-        <v>6760557.878418777</v>
+        <v>6760603</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,22 +1451,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lever i de fuktiga markerna på flera ställen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,21 +1470,222 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Hedvig Martin Ahlen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hedvig Martin Ahlen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99292030</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spaksjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558051</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6760621</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svartnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-05-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-05-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hedvig Martin Ahlen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hedvig Martin Ahlen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104945520</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>norr om Spaksjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6760558</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svartnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
